--- a/outputs/analysis/channel_roi.xlsx
+++ b/outputs/analysis/channel_roi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="70">
   <si>
     <t>Channel</t>
   </si>
@@ -49,15 +49,42 @@
     <t>Channel Spend ($)</t>
   </si>
   <si>
-    <t>Pipeline ROI (x)</t>
-  </si>
-  <si>
-    <t>Revenue ROI (x)</t>
+    <t>Recorded Pipeline / Tracked Spend (x)</t>
+  </si>
+  <si>
+    <t>Recorded Won Amount / Tracked Spend (x)</t>
   </si>
   <si>
     <t>Cost per Opp ($)</t>
   </si>
   <si>
+    <t>spend_measurement_status</t>
+  </si>
+  <si>
+    <t>spend_period_start</t>
+  </si>
+  <si>
+    <t>spend_period_end</t>
+  </si>
+  <si>
+    <t>pipeline_period_start</t>
+  </si>
+  <si>
+    <t>pipeline_period_end</t>
+  </si>
+  <si>
+    <t>period_matched_pipeline</t>
+  </si>
+  <si>
+    <t>period_matched_won_amount</t>
+  </si>
+  <si>
+    <t>period_matched_opportunities</t>
+  </si>
+  <si>
+    <t>ratio_definition</t>
+  </si>
+  <si>
     <t>other</t>
   </si>
   <si>
@@ -79,12 +106,12 @@
     <t>6sense_event</t>
   </si>
   <si>
+    <t>6sense_display</t>
+  </si>
+  <si>
     <t>email_mqa</t>
   </si>
   <si>
-    <t>6sense_display</t>
-  </si>
-  <si>
     <t>webinar</t>
   </si>
   <si>
@@ -97,13 +124,13 @@
     <t>22.4%</t>
   </si>
   <si>
-    <t>57.1%</t>
+    <t>57.0%</t>
   </si>
   <si>
     <t>32.6%</t>
   </si>
   <si>
-    <t>13.6%</t>
+    <t>13.7%</t>
   </si>
   <si>
     <t>23.1%</t>
@@ -118,55 +145,49 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>1.2%</t>
-  </si>
-  <si>
     <t>33.3%</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>77.9%</t>
-  </si>
-  <si>
-    <t>95.1%</t>
+    <t>78.8%</t>
+  </si>
+  <si>
+    <t>95.5%</t>
   </si>
   <si>
     <t>88.7%</t>
   </si>
   <si>
-    <t>88.8%</t>
-  </si>
-  <si>
-    <t>87.4%</t>
-  </si>
-  <si>
-    <t>77.3%</t>
+    <t>90.4%</t>
+  </si>
+  <si>
+    <t>79.1%</t>
   </si>
   <si>
     <t>73.2%</t>
   </si>
   <si>
-    <t>51.1%</t>
-  </si>
-  <si>
-    <t>95.6%</t>
+    <t>98.8%</t>
+  </si>
+  <si>
+    <t>55.4%</t>
   </si>
   <si>
     <t>85.7%</t>
   </si>
   <si>
-    <t>59.2%</t>
-  </si>
-  <si>
-    <t>12.8%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>6.1%</t>
+    <t>59.3%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>11.3%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
   </si>
   <si>
     <t>4.4%</t>
@@ -185,6 +206,24 @@
   </si>
   <si>
     <t>0.1%</t>
+  </si>
+  <si>
+    <t>unmeasured</t>
+  </si>
+  <si>
+    <t>tracked</t>
+  </si>
+  <si>
+    <t>2023-01-31T08:55:01+00:00</t>
+  </si>
+  <si>
+    <t>2023-09-11T02:36:59+00:00</t>
+  </si>
+  <si>
+    <t>2024-10-07T01:20:57+00:00</t>
+  </si>
+  <si>
+    <t>Recorded same-period sourced pipeline / tracked platform spend; descriptive, not incremental ROI</t>
   </si>
 </sst>
 </file>
@@ -516,10 +555,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,19 +601,46 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>1120</v>
+        <v>1104</v>
       </c>
       <c r="C2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D2">
-        <v>14813748.66</v>
+        <v>14753748.66</v>
       </c>
       <c r="E2">
         <v>2456816.16</v>
@@ -583,65 +649,65 @@
         <v>195</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I2">
-        <v>13273.96833333333</v>
+        <v>13363.90277173913</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>54</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="C3">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="D3">
-        <v>3188158.65</v>
+        <v>3158158.65</v>
       </c>
       <c r="E3">
-        <v>1172387.77</v>
+        <v>1162387.77</v>
       </c>
       <c r="F3">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>2333.93751830161</v>
+        <v>2325.595471281296</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>291</v>
@@ -659,33 +725,33 @@
         <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I4">
         <v>9642.852233676977</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>56</v>
+      </c>
+      <c r="O4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>1535086</v>
@@ -697,36 +763,36 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I5">
-        <v>13233.5</v>
+        <v>13348.57391304348</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>57</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>104</v>
       </c>
       <c r="D6">
-        <v>1100230</v>
+        <v>1090230</v>
       </c>
       <c r="E6">
         <v>294824</v>
@@ -735,30 +801,30 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>9245.63025210084</v>
+        <v>9480.260869565218</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>58</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="W6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -773,27 +839,27 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I7">
-        <v>15402.84090909091</v>
+        <v>15761.04651162791</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
+        <v>64</v>
+      </c>
+      <c r="W7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>41</v>
@@ -811,36 +877,36 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I8">
         <v>15243.68292682927</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>60</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C9">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="D9">
-        <v>91226.5</v>
+        <v>89016</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -849,71 +915,98 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I9">
-        <v>991.5923913043479</v>
+        <v>1035.06976744186</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K9">
+        <v>1186809.5</v>
+      </c>
+      <c r="L9">
+        <v>0.0750044552221734</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>14651.96913580247</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" t="s">
+        <v>68</v>
+      </c>
+      <c r="T9">
+        <v>89016</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>81</v>
+      </c>
+      <c r="W9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C10">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="D10">
-        <v>89016</v>
+        <v>57033</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I10">
-        <v>989.0666666666667</v>
+        <v>687.144578313253</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10">
-        <v>1186809.5</v>
-      </c>
-      <c r="L10">
-        <v>0.08</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>13186.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>62</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+      <c r="W10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -931,27 +1024,27 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I11">
         <v>5604.571428571428</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>62</v>
+      </c>
+      <c r="O11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -969,33 +1062,57 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I12">
         <v>30000</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K12">
         <v>34546.99</v>
       </c>
       <c r="L12">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12">
-        <v>34546.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" t="s">
+        <v>67</v>
+      </c>
+      <c r="S12" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1013,22 +1130,22 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I13">
         <v>15409</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="O13" t="s">
+        <v>64</v>
+      </c>
+      <c r="W13" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
